--- a/Testing Input and Output Files/output_for_testing_SL_hours_by_asset_opDay.xlsx
+++ b/Testing Input and Output Files/output_for_testing_SL_hours_by_asset_opDay.xlsx
@@ -7856,7 +7856,7 @@
         <v>46388</v>
       </c>
       <c r="C571" t="n">
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="572">
@@ -7960,7 +7960,7 @@
         <v>46478</v>
       </c>
       <c r="C579" t="n">
-        <v>21.6</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="580">
@@ -8207,7 +8207,7 @@
         <v>46569</v>
       </c>
       <c r="C598" t="n">
-        <v>22.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="599">
@@ -8441,7 +8441,7 @@
         <v>46660</v>
       </c>
       <c r="C616" t="n">
-        <v>22.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="617">
@@ -17606,7 +17606,7 @@
         <v>46414</v>
       </c>
       <c r="C1321" t="n">
-        <v>9.600000000000001</v>
+        <v>4.800000000000001</v>
       </c>
     </row>
     <row r="1322">
@@ -17619,7 +17619,7 @@
         <v>46415</v>
       </c>
       <c r="C1322" t="n">
-        <v>9.600000000000001</v>
+        <v>4.800000000000001</v>
       </c>
     </row>
     <row r="1323">
@@ -17632,7 +17632,7 @@
         <v>46416</v>
       </c>
       <c r="C1323" t="n">
-        <v>9.600000000000001</v>
+        <v>4.800000000000001</v>
       </c>
     </row>
     <row r="1324">
@@ -17645,7 +17645,7 @@
         <v>46417</v>
       </c>
       <c r="C1324" t="n">
-        <v>9.600000000000001</v>
+        <v>4.800000000000001</v>
       </c>
     </row>
     <row r="1325">
@@ -57503,7 +57503,7 @@
         <v>46530</v>
       </c>
       <c r="C4390" t="n">
-        <v>7.600000000000001</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4391">
